--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,6 +1592,2090 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131860492</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>535039</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6721992</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131856439</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>534895</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6721975</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131860837</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58552</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>535021</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6721985</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131931659</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>534931</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6721980</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131861178</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>534975</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6722036</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131935328</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>534911</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6721960</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131856731</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>534891</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6721970</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131934412</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99045</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>535044</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6722017</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131937568</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99045</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>535010</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6721978</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131857452</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6721978</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131856819</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>534891</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6721970</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>i tallåga.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131934104</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93127</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535034</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6722021</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131855987</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8454</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>534881</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6722022</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Område som gjorts naturvårdsbränning i</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131854070</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99045</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>534834</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6721994</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Jag kan ange exakta koordinater.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131932040</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99045</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>534978</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6722023</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131933678</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99045</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>535032</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6722043</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131932494</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>534986</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6722058</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131932788</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>535003</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6722088</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -2511,54 +2511,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131937568</v>
+        <v>131857452</v>
       </c>
       <c r="B18" t="n">
-        <v>99045</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535010</v>
+        <v>534901</v>
       </c>
       <c r="R18" t="n">
         <v>6721978</v>
@@ -2588,22 +2584,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,7 +2613,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2624,49 +2624,46 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131857452</v>
+        <v>131856819</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>8454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2674,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534901</v>
+        <v>534891</v>
       </c>
       <c r="R19" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,12 +2716,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,6 +2730,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2751,50 +2749,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131856819</v>
+        <v>131937568</v>
       </c>
       <c r="B20" t="n">
-        <v>8454</v>
+        <v>99045</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534891</v>
+        <v>535010</v>
       </c>
       <c r="R20" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,27 +2826,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>i tallåga.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -2511,50 +2511,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131857452</v>
+        <v>131937568</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>99045</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534901</v>
+        <v>535010</v>
       </c>
       <c r="R18" t="n">
         <v>6721978</v>
@@ -2584,27 +2588,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,6 +2612,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2624,46 +2624,49 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131856819</v>
+        <v>131857452</v>
       </c>
       <c r="B19" t="n">
-        <v>8454</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2671,10 +2674,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534891</v>
+        <v>534901</v>
       </c>
       <c r="R19" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2709,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,12 +2719,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>i tallåga.</t>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,7 +2733,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2749,57 +2751,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131937568</v>
+        <v>131856819</v>
       </c>
       <c r="B20" t="n">
-        <v>99045</v>
+        <v>8454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535010</v>
+        <v>534891</v>
       </c>
       <c r="R20" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,22 +2821,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,17 +2862,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131934104</v>
+        <v>131855987</v>
       </c>
       <c r="B21" t="n">
-        <v>93127</v>
+        <v>8454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,37 +2880,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535034</v>
+        <v>534881</v>
       </c>
       <c r="R21" t="n">
-        <v>6722021</v>
+        <v>6722022</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,22 +2934,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Område som gjorts naturvårdsbränning i</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,7 +2963,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2973,17 +2974,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131855987</v>
+        <v>131934104</v>
       </c>
       <c r="B22" t="n">
-        <v>8454</v>
+        <v>93127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2991,34 +2992,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534881</v>
+        <v>535034</v>
       </c>
       <c r="R22" t="n">
-        <v>6722022</v>
+        <v>6722021</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,27 +3049,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Område som gjorts naturvårdsbränning i</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,6 +3073,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1594,42 +1594,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860492</v>
+        <v>131856439</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1637,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535039</v>
+        <v>534895</v>
       </c>
       <c r="R10" t="n">
-        <v>6721992</v>
+        <v>6721975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,12 +1679,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
+          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1714,39 +1712,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131856439</v>
+        <v>131860492</v>
       </c>
       <c r="B11" t="n">
-        <v>8454</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534895</v>
+        <v>535039</v>
       </c>
       <c r="R11" t="n">
-        <v>6721975</v>
+        <v>6721992</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,12 +1800,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
+          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,7 +1814,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>131860837</v>
       </c>
       <c r="B12" t="n">
-        <v>58552</v>
+        <v>58554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>131931659</v>
       </c>
       <c r="B13" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>131861178</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131935328</v>
       </c>
       <c r="B15" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>131856731</v>
       </c>
       <c r="B16" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131934412</v>
       </c>
       <c r="B17" t="n">
-        <v>99045</v>
+        <v>99047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>131937568</v>
       </c>
       <c r="B18" t="n">
-        <v>99045</v>
+        <v>99047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>131857452</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>131856819</v>
       </c>
       <c r="B20" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>131855987</v>
       </c>
       <c r="B21" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>131934104</v>
       </c>
       <c r="B22" t="n">
-        <v>93127</v>
+        <v>93129</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>131854070</v>
       </c>
       <c r="B23" t="n">
-        <v>99045</v>
+        <v>99047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>131932040</v>
       </c>
       <c r="B24" t="n">
-        <v>99045</v>
+        <v>99047</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>131933678</v>
       </c>
       <c r="B25" t="n">
-        <v>99045</v>
+        <v>99047</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>131932494</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>131932788</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1594,39 +1594,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131856439</v>
+        <v>131860492</v>
       </c>
       <c r="B10" t="n">
-        <v>8455</v>
+        <v>57909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1634,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534895</v>
+        <v>535039</v>
       </c>
       <c r="R10" t="n">
-        <v>6721975</v>
+        <v>6721992</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,12 +1682,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
+          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1696,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1712,42 +1714,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131860492</v>
+        <v>131856439</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1755,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535039</v>
+        <v>534895</v>
       </c>
       <c r="R11" t="n">
-        <v>6721992</v>
+        <v>6721975</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,12 +1799,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
+          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,6 +1813,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,56 +1832,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860837</v>
+        <v>131931659</v>
       </c>
       <c r="B12" t="n">
-        <v>58554</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535021</v>
+        <v>534931</v>
       </c>
       <c r="R12" t="n">
-        <v>6721985</v>
+        <v>6721980</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,22 +1897,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,48 +1944,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131931659</v>
+        <v>131860837</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>58559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534931</v>
+        <v>535021</v>
       </c>
       <c r="R13" t="n">
-        <v>6721980</v>
+        <v>6721985</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,27 +2017,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kammossa vitmossor skvattram</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,7 +2062,7 @@
         <v>131861178</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131934412</v>
       </c>
       <c r="B17" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,57 +2511,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131937568</v>
+        <v>131856819</v>
       </c>
       <c r="B18" t="n">
-        <v>99047</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535010</v>
+        <v>534891</v>
       </c>
       <c r="R18" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,22 +2581,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,57 +2622,61 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131857452</v>
+        <v>131937568</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>99052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534901</v>
+        <v>535010</v>
       </c>
       <c r="R19" t="n">
         <v>6721978</v>
@@ -2704,27 +2706,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,6 +2730,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2744,46 +2742,49 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131856819</v>
+        <v>131857452</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>57909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2791,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534891</v>
+        <v>534901</v>
       </c>
       <c r="R20" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,12 +2837,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>i tallåga.</t>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,7 +2851,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131855987</v>
+        <v>131934104</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>93134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,34 +2880,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534881</v>
+        <v>535034</v>
       </c>
       <c r="R21" t="n">
-        <v>6722022</v>
+        <v>6722021</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2934,27 +2937,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Område som gjorts naturvårdsbränning i</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,6 +2961,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2974,17 +2973,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131934104</v>
+        <v>131855987</v>
       </c>
       <c r="B22" t="n">
-        <v>93129</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,37 +2991,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535034</v>
+        <v>534881</v>
       </c>
       <c r="R22" t="n">
-        <v>6722021</v>
+        <v>6722022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,22 +3045,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Område som gjorts naturvårdsbränning i</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,7 +3074,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3095,7 +3095,7 @@
         <v>131854070</v>
       </c>
       <c r="B23" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>131932040</v>
       </c>
       <c r="B24" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>131933678</v>
       </c>
       <c r="B25" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>131932494</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>131932788</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1594,42 +1594,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860492</v>
+        <v>131856439</v>
       </c>
       <c r="B10" t="n">
-        <v>57909</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1637,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535039</v>
+        <v>534895</v>
       </c>
       <c r="R10" t="n">
-        <v>6721992</v>
+        <v>6721975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,12 +1679,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
+          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1714,39 +1712,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131856439</v>
+        <v>131860492</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>57909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534895</v>
+        <v>535039</v>
       </c>
       <c r="R11" t="n">
-        <v>6721975</v>
+        <v>6721992</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,12 +1800,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
+          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,7 +1814,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,48 +1832,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131931659</v>
+        <v>131860837</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>58559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534931</v>
+        <v>535021</v>
       </c>
       <c r="R12" t="n">
-        <v>6721980</v>
+        <v>6721985</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,27 +1905,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kammossa vitmossor skvattram</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,56 +1947,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131860837</v>
+        <v>131931659</v>
       </c>
       <c r="B13" t="n">
-        <v>58559</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103042</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535021</v>
+        <v>534931</v>
       </c>
       <c r="R13" t="n">
-        <v>6721985</v>
+        <v>6721980</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,22 +2012,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2511,39 +2511,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131856819</v>
+        <v>131857452</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>57909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2551,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534891</v>
+        <v>534901</v>
       </c>
       <c r="R18" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,12 +2599,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>i tallåga.</t>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,7 +2613,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2749,42 +2751,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131857452</v>
+        <v>131856819</v>
       </c>
       <c r="B20" t="n">
-        <v>57909</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2792,10 +2791,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534901</v>
+        <v>534891</v>
       </c>
       <c r="R20" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,7 +2826,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,12 +2836,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,6 +2850,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1835,7 +1835,7 @@
         <v>131860837</v>
       </c>
       <c r="B12" t="n">
-        <v>58595</v>
+        <v>58597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131934412</v>
       </c>
       <c r="B17" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,39 +2511,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131856819</v>
+        <v>131857452</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2551,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534891</v>
+        <v>534901</v>
       </c>
       <c r="R18" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,12 +2599,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>i tallåga.</t>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,7 +2613,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2629,57 +2631,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131937568</v>
+        <v>131856819</v>
       </c>
       <c r="B19" t="n">
-        <v>99095</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535010</v>
+        <v>534891</v>
       </c>
       <c r="R19" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,22 +2701,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,57 +2742,61 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131857452</v>
+        <v>131937568</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534901</v>
+        <v>535010</v>
       </c>
       <c r="R20" t="n">
         <v>6721978</v>
@@ -2822,27 +2826,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,6 +2850,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
         <v>131934104</v>
       </c>
       <c r="B22" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>131854070</v>
       </c>
       <c r="B23" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>131932040</v>
       </c>
       <c r="B24" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>131933678</v>
       </c>
       <c r="B25" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131932788</v>
+        <v>131932494</v>
       </c>
       <c r="B26" t="n">
         <v>57945</v>
@@ -3481,7 +3481,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535003</v>
+        <v>534986</v>
       </c>
       <c r="R26" t="n">
-        <v>6722088</v>
+        <v>6722058</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131932494</v>
+        <v>131932788</v>
       </c>
       <c r="B27" t="n">
         <v>57945</v>
@@ -3596,7 +3596,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534986</v>
+        <v>535003</v>
       </c>
       <c r="R27" t="n">
-        <v>6722058</v>
+        <v>6722088</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1832,56 +1832,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860837</v>
+        <v>131931659</v>
       </c>
       <c r="B12" t="n">
-        <v>58597</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535021</v>
+        <v>534931</v>
       </c>
       <c r="R12" t="n">
-        <v>6721985</v>
+        <v>6721980</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,22 +1897,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,48 +1944,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131931659</v>
+        <v>131860837</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>58597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534931</v>
+        <v>535021</v>
       </c>
       <c r="R13" t="n">
-        <v>6721980</v>
+        <v>6721985</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,27 +2017,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kammossa vitmossor skvattram</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2631,50 +2631,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131856819</v>
+        <v>131937568</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>99098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534891</v>
+        <v>535010</v>
       </c>
       <c r="R19" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2701,27 +2708,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>i tallåga.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,64 +2744,57 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131937568</v>
+        <v>131856819</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535010</v>
+        <v>534891</v>
       </c>
       <c r="R20" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,22 +2821,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131932494</v>
+        <v>131932788</v>
       </c>
       <c r="B26" t="n">
         <v>57945</v>
@@ -3481,7 +3481,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534986</v>
+        <v>535003</v>
       </c>
       <c r="R26" t="n">
-        <v>6722058</v>
+        <v>6722088</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131932788</v>
+        <v>131932494</v>
       </c>
       <c r="B27" t="n">
         <v>57945</v>
@@ -3596,7 +3596,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535003</v>
+        <v>534986</v>
       </c>
       <c r="R27" t="n">
-        <v>6722088</v>
+        <v>6722058</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -3448,7 +3448,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131932788</v>
+        <v>131932494</v>
       </c>
       <c r="B26" t="n">
         <v>57945</v>
@@ -3481,7 +3481,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535003</v>
+        <v>534986</v>
       </c>
       <c r="R26" t="n">
-        <v>6722088</v>
+        <v>6722058</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131932494</v>
+        <v>131932788</v>
       </c>
       <c r="B27" t="n">
         <v>57945</v>
@@ -3596,7 +3596,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534986</v>
+        <v>535003</v>
       </c>
       <c r="R27" t="n">
-        <v>6722058</v>
+        <v>6722088</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1597,7 +1597,7 @@
         <v>131860492</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>131860837</v>
       </c>
       <c r="B13" t="n">
-        <v>58597</v>
+        <v>58598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>131861178</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131934412</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,42 +2511,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131857452</v>
+        <v>131856819</v>
       </c>
       <c r="B18" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2554,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534901</v>
+        <v>534891</v>
       </c>
       <c r="R18" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,12 +2596,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,6 +2610,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2631,54 +2629,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131937568</v>
+        <v>131857452</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>57946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535010</v>
+        <v>534901</v>
       </c>
       <c r="R19" t="n">
         <v>6721978</v>
@@ -2708,22 +2702,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,7 +2731,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2744,57 +2742,64 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131856819</v>
+        <v>131937568</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>99106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534891</v>
+        <v>535010</v>
       </c>
       <c r="R20" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,27 +2826,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>i tallåga.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,17 +2862,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131855987</v>
+        <v>131934104</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>93186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,34 +2880,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534881</v>
+        <v>535034</v>
       </c>
       <c r="R21" t="n">
-        <v>6722022</v>
+        <v>6722021</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2934,27 +2937,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Område som gjorts naturvårdsbränning i</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,6 +2961,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2974,17 +2973,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131934104</v>
+        <v>131855987</v>
       </c>
       <c r="B22" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,37 +2991,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535034</v>
+        <v>534881</v>
       </c>
       <c r="R22" t="n">
-        <v>6722021</v>
+        <v>6722022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,22 +3045,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Område som gjorts naturvårdsbränning i</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,7 +3074,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3095,7 +3095,7 @@
         <v>131854070</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>131932040</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>131933678</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>131932494</v>
       </c>
       <c r="B26" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>131932788</v>
       </c>
       <c r="B27" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -2511,50 +2511,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131856819</v>
+        <v>131937568</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>99106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534891</v>
+        <v>535010</v>
       </c>
       <c r="R18" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,27 +2588,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>i tallåga.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,7 +2624,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2749,57 +2751,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131937568</v>
+        <v>131856819</v>
       </c>
       <c r="B20" t="n">
-        <v>99106</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535010</v>
+        <v>534891</v>
       </c>
       <c r="R20" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,22 +2821,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1597,7 +1597,7 @@
         <v>131860492</v>
       </c>
       <c r="B10" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1832,48 +1832,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131931659</v>
+        <v>131860837</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>58602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534931</v>
+        <v>535021</v>
       </c>
       <c r="R12" t="n">
-        <v>6721980</v>
+        <v>6721985</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,27 +1905,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kammossa vitmossor skvattram</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,56 +1947,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131860837</v>
+        <v>131931659</v>
       </c>
       <c r="B13" t="n">
-        <v>58598</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103042</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535021</v>
+        <v>534931</v>
       </c>
       <c r="R13" t="n">
-        <v>6721985</v>
+        <v>6721980</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,22 +2012,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,7 +2062,7 @@
         <v>131861178</v>
       </c>
       <c r="B14" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131934412</v>
       </c>
       <c r="B17" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,54 +2511,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131937568</v>
+        <v>131857452</v>
       </c>
       <c r="B18" t="n">
-        <v>99106</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535010</v>
+        <v>534901</v>
       </c>
       <c r="R18" t="n">
         <v>6721978</v>
@@ -2588,22 +2584,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,7 +2613,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2624,49 +2624,46 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131857452</v>
+        <v>131856819</v>
       </c>
       <c r="B19" t="n">
-        <v>57946</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2674,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534901</v>
+        <v>534891</v>
       </c>
       <c r="R19" t="n">
-        <v>6721978</v>
+        <v>6721970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,12 +2716,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,6 +2730,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2751,50 +2749,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131856819</v>
+        <v>131937568</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>99116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534891</v>
+        <v>535010</v>
       </c>
       <c r="R20" t="n">
-        <v>6721970</v>
+        <v>6721978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,27 +2826,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>i tallåga.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,17 +2862,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131934104</v>
+        <v>131855987</v>
       </c>
       <c r="B21" t="n">
-        <v>93186</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,37 +2880,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535034</v>
+        <v>534881</v>
       </c>
       <c r="R21" t="n">
-        <v>6722021</v>
+        <v>6722022</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,22 +2934,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Område som gjorts naturvårdsbränning i</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,7 +2963,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2973,17 +2974,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131855987</v>
+        <v>131934104</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>93196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2991,34 +2992,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534881</v>
+        <v>535034</v>
       </c>
       <c r="R22" t="n">
-        <v>6722022</v>
+        <v>6722021</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,27 +3049,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Område som gjorts naturvårdsbränning i</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,6 +3073,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3095,7 +3095,7 @@
         <v>131854070</v>
       </c>
       <c r="B23" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>131932040</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>131933678</v>
       </c>
       <c r="B25" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131932494</v>
+        <v>131932788</v>
       </c>
       <c r="B26" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534986</v>
+        <v>535003</v>
       </c>
       <c r="R26" t="n">
-        <v>6722058</v>
+        <v>6722088</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131932788</v>
+        <v>131932494</v>
       </c>
       <c r="B27" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535003</v>
+        <v>534986</v>
       </c>
       <c r="R27" t="n">
-        <v>6722088</v>
+        <v>6722058</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -1832,56 +1832,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131860837</v>
+        <v>131931659</v>
       </c>
       <c r="B12" t="n">
-        <v>58602</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535021</v>
+        <v>534931</v>
       </c>
       <c r="R12" t="n">
-        <v>6721985</v>
+        <v>6721980</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,22 +1897,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,48 +1944,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131931659</v>
+        <v>131860837</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>58602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534931</v>
+        <v>535021</v>
       </c>
       <c r="R13" t="n">
-        <v>6721980</v>
+        <v>6721985</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,27 +2017,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kammossa vitmossor skvattram</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3448,7 +3448,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131932788</v>
+        <v>131932494</v>
       </c>
       <c r="B26" t="n">
         <v>57950</v>
@@ -3481,7 +3481,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535003</v>
+        <v>534986</v>
       </c>
       <c r="R26" t="n">
-        <v>6722088</v>
+        <v>6722058</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131932494</v>
+        <v>131932788</v>
       </c>
       <c r="B27" t="n">
         <v>57950</v>
@@ -3596,7 +3596,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534986</v>
+        <v>535003</v>
       </c>
       <c r="R27" t="n">
-        <v>6722058</v>
+        <v>6722088</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3676,6 +3676,225 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132670982</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>534968</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6722066</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Orrspelet hörs tydligt när trafiken gör avbrott</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132670790</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>534906</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6721984</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -3681,7 +3681,7 @@
         <v>132670982</v>
       </c>
       <c r="B28" t="n">
-        <v>57145</v>
+        <v>57148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>132670790</v>
       </c>
       <c r="B29" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3895,6 +3895,224 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133140857</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>535045</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6721981</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133139617</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92647</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>757</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Apelsinticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hapalopilus aurantiacus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>535027</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6721978</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4113,6 +4113,113 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133139883</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>535041</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6721981</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -3897,10 +3897,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133140857</v>
+        <v>133139617</v>
       </c>
       <c r="B30" t="n">
-        <v>57954</v>
+        <v>92648</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3908,34 +3908,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>757</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535045</v>
+        <v>535027</v>
       </c>
       <c r="R30" t="n">
-        <v>6721981</v>
+        <v>6721978</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3967,7 +3970,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3977,15 +3980,16 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4004,10 +4008,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133139617</v>
+        <v>133140857</v>
       </c>
       <c r="B31" t="n">
-        <v>92647</v>
+        <v>57954</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,37 +4019,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>757</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535027</v>
+        <v>535045</v>
       </c>
       <c r="R31" t="n">
-        <v>6721978</v>
+        <v>6721981</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,7 +4078,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4087,16 +4088,15 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -3793,7 +3793,7 @@
         <v>132670790</v>
       </c>
       <c r="B29" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133139617</v>
+        <v>133140857</v>
       </c>
       <c r="B30" t="n">
-        <v>92648</v>
+        <v>57955</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3908,37 +3908,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>757</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535027</v>
+        <v>535045</v>
       </c>
       <c r="R30" t="n">
-        <v>6721978</v>
+        <v>6721981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3970,7 +3967,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3980,16 +3977,15 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4008,10 +4004,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133140857</v>
+        <v>133139617</v>
       </c>
       <c r="B31" t="n">
-        <v>57954</v>
+        <v>92649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,34 +4015,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>757</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535045</v>
+        <v>535027</v>
       </c>
       <c r="R31" t="n">
-        <v>6721981</v>
+        <v>6721978</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4078,7 +4077,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4088,15 +4087,16 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69624301</v>
+        <v>133139617</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnet, Dlr</t>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535033.8917613621</v>
+        <v>535027</v>
       </c>
       <c r="R2" t="n">
-        <v>6721982.764191089</v>
+        <v>6721978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,95 +743,94 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69624299</v>
+        <v>119120258</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnet, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534931.1676549015</v>
+        <v>534858</v>
       </c>
       <c r="R3" t="n">
-        <v>6721932.203499513</v>
+        <v>6722027</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +854,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nio från i år och en från förra året. På Falu kommuns mark där de genomförde en naturvårdsbränning för 8-10 år sedan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,71 +883,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69624302</v>
+        <v>119550635</v>
       </c>
       <c r="B4" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534940.8739331317</v>
+        <v>535033</v>
       </c>
       <c r="R4" t="n">
-        <v>6722046.14117248</v>
+        <v>6721962</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,62 +997,71 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115734062</v>
+        <v>119623105</v>
       </c>
       <c r="B5" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jungfruberget (Jungfruberget), Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534847</v>
+        <v>534870</v>
       </c>
       <c r="R5" t="n">
-        <v>6722012</v>
+        <v>6722037</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1081,22 +1088,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1118,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119120258</v>
+        <v>131934104</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1166,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534858</v>
+        <v>535034</v>
       </c>
       <c r="R6" t="n">
-        <v>6722027</v>
+        <v>6722021</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,27 +1198,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Nio från i år och en från förra året. På Falu kommuns mark där de genomförde en naturvårdsbränning för 8-10 år sedan.</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119119706</v>
+        <v>131931750</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,37 +1252,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534840</v>
+        <v>534974</v>
       </c>
       <c r="R7" t="n">
-        <v>6722003</v>
+        <v>6721990</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,22 +1313,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,55 +1337,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119623105</v>
+        <v>133142883</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1399,98 +1394,91 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Backen TT, Backen TT, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534870</v>
+        <v>534896</v>
       </c>
       <c r="R8" t="n">
-        <v>6722037</v>
+        <v>6721928</v>
       </c>
       <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
         <v>1</v>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119550635</v>
+        <v>115733713</v>
       </c>
       <c r="B9" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,37 +1486,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535033</v>
+        <v>534819</v>
       </c>
       <c r="R9" t="n">
-        <v>6721962</v>
+        <v>6722009</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,22 +1544,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Östra gränsen. Hack runt om.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,14 +1591,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131860492</v>
+        <v>115734365</v>
       </c>
       <c r="B10" t="n">
         <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1637,13 +1634,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535039</v>
+        <v>534810</v>
       </c>
       <c r="R10" t="n">
-        <v>6721992</v>
+        <v>6722014</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,27 +1664,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
+          <t>död klen tall stående tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131856439</v>
+        <v>115734466</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,28 +1722,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534895</v>
+        <v>534801</v>
       </c>
       <c r="R11" t="n">
-        <v>6721975</v>
+        <v>6722014</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,36 +1784,35 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
+          <t>Klen tall med brott ovan jord, den lutar mot en klen gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,55 +1831,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131931750</v>
+        <v>115734662</v>
       </c>
       <c r="B12" t="n">
-        <v>91981</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534974</v>
+        <v>534794</v>
       </c>
       <c r="R12" t="n">
-        <v>6721990</v>
+        <v>6722008</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,22 +1904,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Blött!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,29 +1933,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131931659</v>
+        <v>115735183</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,37 +1962,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534931</v>
+        <v>534789</v>
       </c>
       <c r="R13" t="n">
-        <v>6721980</v>
+        <v>6722026</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,27 +2024,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kammossa vitmossor skvattram</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,27 +2066,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131860837</v>
+        <v>115735661</v>
       </c>
       <c r="B14" t="n">
-        <v>58602</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2092,7 +2099,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2102,13 +2109,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535021</v>
+        <v>534796</v>
       </c>
       <c r="R14" t="n">
-        <v>6721985</v>
+        <v>6722027</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2132,22 +2139,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,14 +2181,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131861178</v>
+        <v>115735802</v>
       </c>
       <c r="B15" t="n">
         <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2217,13 +2224,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534975</v>
+        <v>534782</v>
       </c>
       <c r="R15" t="n">
-        <v>6722036</v>
+        <v>6722050</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2247,22 +2254,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2296,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131935328</v>
+        <v>116708002</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,42 +2307,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534911</v>
+        <v>534817</v>
       </c>
       <c r="R16" t="n">
-        <v>6721960</v>
+        <v>6721998</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2359,22 +2365,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>04:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>04:38</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4:38 Oerhört vackert med orrspel i norr och soluppgång i öst.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,7 +2394,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2405,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131856731</v>
+        <v>119119706</v>
       </c>
       <c r="B17" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,42 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534891</v>
+        <v>534840</v>
       </c>
       <c r="R17" t="n">
-        <v>6721970</v>
+        <v>6722003</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2472,22 +2477,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,7 +2501,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2515,49 +2519,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131934412</v>
+        <v>131857452</v>
       </c>
       <c r="B18" t="n">
-        <v>99116</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535044</v>
+        <v>534901</v>
       </c>
       <c r="R18" t="n">
-        <v>6722017</v>
+        <v>6721978</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,22 +2592,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,26 +2627,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131857452</v>
+        <v>131860492</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2669,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534901</v>
+        <v>535039</v>
       </c>
       <c r="R19" t="n">
-        <v>6721978</v>
+        <v>6721992</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2704,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2714,12 +2727,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2746,10 +2759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131856819</v>
+        <v>131861178</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,28 +2770,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2786,10 +2802,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534891</v>
+        <v>534975</v>
       </c>
       <c r="R20" t="n">
-        <v>6721970</v>
+        <v>6722036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,7 +2837,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,12 +2847,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>i tallåga.</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,7 +2856,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2864,60 +2874,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131937568</v>
+        <v>131932494</v>
       </c>
       <c r="B21" t="n">
-        <v>99116</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535010</v>
+        <v>534986</v>
       </c>
       <c r="R21" t="n">
-        <v>6721978</v>
+        <v>6722058</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2946,7 +2952,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2962,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,7 +2971,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2984,10 +2989,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131855987</v>
+        <v>131932788</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,37 +3000,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534881</v>
+        <v>535003</v>
       </c>
       <c r="R22" t="n">
-        <v>6722022</v>
+        <v>6722088</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3049,27 +3062,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Område som gjorts naturvårdsbränning i</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,17 +3097,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131934104</v>
+        <v>131933786</v>
       </c>
       <c r="B23" t="n">
-        <v>93196</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3107,37 +3115,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535034</v>
+        <v>535060</v>
       </c>
       <c r="R23" t="n">
-        <v>6722021</v>
+        <v>6722004</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3179,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,76 +3193,63 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131854070</v>
+        <v>132670790</v>
       </c>
       <c r="B24" t="n">
-        <v>99116</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534834</v>
+        <v>534906</v>
       </c>
       <c r="R24" t="n">
-        <v>6721994</v>
+        <v>6721984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,27 +3276,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Jag kan ange exakta koordinater.</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3313,7 +3300,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3332,49 +3318,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131932040</v>
+        <v>133140857</v>
       </c>
       <c r="B25" t="n">
-        <v>99116</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534978</v>
+        <v>535045</v>
       </c>
       <c r="R25" t="n">
-        <v>6722023</v>
+        <v>6721981</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,22 +3383,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,58 +3413,54 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131933678</v>
+        <v>133430533</v>
       </c>
       <c r="B26" t="n">
-        <v>99116</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3490,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535032</v>
+        <v>534834</v>
       </c>
       <c r="R26" t="n">
-        <v>6722043</v>
+        <v>6722003</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3520,22 +3498,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,7 +3522,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3556,21 +3533,21 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131932494</v>
+        <v>133701691</v>
       </c>
       <c r="B27" t="n">
-        <v>57950</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3602,14 +3579,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534986</v>
+        <v>534875</v>
       </c>
       <c r="R27" t="n">
-        <v>6722058</v>
+        <v>6721945</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3636,22 +3613,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3671,63 +3648,59 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131932788</v>
+        <v>133701658</v>
       </c>
       <c r="B28" t="n">
-        <v>57950</v>
+        <v>57967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535003</v>
+        <v>534898</v>
       </c>
       <c r="R28" t="n">
-        <v>6722088</v>
+        <v>6721903</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3751,22 +3724,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,17 +3759,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132670982</v>
+        <v>115734062</v>
       </c>
       <c r="B29" t="n">
-        <v>57148</v>
+        <v>5179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,34 +3777,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534968</v>
+        <v>534847</v>
       </c>
       <c r="R29" t="n">
-        <v>6722066</v>
+        <v>6722012</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3858,27 +3831,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:48</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Orrspelet hörs tydligt när trafiken gör avbrott</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3905,45 +3873,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132670790</v>
+        <v>131856731</v>
       </c>
       <c r="B30" t="n">
-        <v>57955</v>
+        <v>5181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534906</v>
+        <v>534891</v>
       </c>
       <c r="R30" t="n">
-        <v>6721984</v>
+        <v>6721970</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3970,22 +3943,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,6 +3967,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4012,51 +3986,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133139617</v>
+        <v>132670982</v>
       </c>
       <c r="B31" t="n">
-        <v>92699</v>
+        <v>57165</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>757</v>
+        <v>102613</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535027</v>
+        <v>534968</v>
       </c>
       <c r="R31" t="n">
-        <v>6721978</v>
+        <v>6722066</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4080,31 +4051,35 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Orrspelet hörs tydligt när trafiken gör avbrott</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4123,27 +4098,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133140857</v>
+        <v>131860402</v>
       </c>
       <c r="B32" t="n">
-        <v>57972</v>
+        <v>58131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103023</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4154,14 +4129,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535045</v>
+        <v>535046</v>
       </c>
       <c r="R32" t="n">
-        <v>6721981</v>
+        <v>6721986</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4188,22 +4163,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4230,10 +4205,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133139883</v>
+        <v>131933329</v>
       </c>
       <c r="B33" t="n">
-        <v>8460</v>
+        <v>58131</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,34 +4216,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535041</v>
+        <v>535029</v>
       </c>
       <c r="R33" t="n">
-        <v>6721981</v>
+        <v>6722040</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4295,22 +4278,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,57 +4313,60 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133526848</v>
+        <v>131860837</v>
       </c>
       <c r="B34" t="n">
-        <v>8460</v>
+        <v>58624</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 4468, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>534896</v>
+        <v>535021</v>
       </c>
       <c r="R34" t="n">
-        <v>6721928</v>
+        <v>6721985</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4407,22 +4393,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4431,7 +4417,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4450,59 +4435,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133142883</v>
+        <v>133701660</v>
       </c>
       <c r="B35" t="n">
-        <v>91981</v>
+        <v>58624</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>103042</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backen TT, Backen TT, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>534896</v>
+        <v>534898</v>
       </c>
       <c r="R35" t="n">
-        <v>6721928</v>
+        <v>6721903</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4531,7 +4509,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4541,16 +4519,15 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4569,27 +4546,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133701691</v>
+        <v>133701664</v>
       </c>
       <c r="B36" t="n">
-        <v>57972</v>
+        <v>58658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4600,11 +4577,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4612,13 +4585,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>534875</v>
+        <v>534898</v>
       </c>
       <c r="R36" t="n">
-        <v>6721945</v>
+        <v>6721903</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4642,22 +4615,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4684,10 +4657,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133701633</v>
+        <v>69624299</v>
       </c>
       <c r="B37" t="n">
-        <v>8460</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4713,21 +4686,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Lugnet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>534890</v>
+        <v>534931</v>
       </c>
       <c r="R37" t="n">
-        <v>6722048</v>
+        <v>6721932</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4754,22 +4722,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>20:31</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>20:31</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4778,72 +4736,63 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133430533</v>
+        <v>69624301</v>
       </c>
       <c r="B38" t="n">
-        <v>57972</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Lugnet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>534834</v>
+        <v>535034</v>
       </c>
       <c r="R38" t="n">
-        <v>6722003</v>
+        <v>6721983</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4870,22 +4819,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4900,15 +4839,1947 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>69624302</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>534941</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6722046</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2017-04-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2017-04-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131855987</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>534881</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6722022</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Område som gjorts naturvårdsbränning i</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131856439</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>534895</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6721975</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131856819</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>534891</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6721970</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>i tallåga.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131931659</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>534931</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6721980</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131935328</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>534911</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6721960</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133139883</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>535041</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6721981</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133526848</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 4468, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>534896</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6721928</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>133701633</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>534890</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6722048</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131854070</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>534834</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6721994</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Jag kan ange exakta koordinater.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131932040</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>534978</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6722023</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131933678</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>535032</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6722043</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131933889</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>535047</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6722041</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131933893</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>535068</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6722008</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131933947</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>535052</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6722014</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131934032</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>535044</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6722017</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131937568</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>535010</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6721978</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133139617</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119120258</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119550635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623105</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934104</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931750</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133142883</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1588,6 +1628,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115733713</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1708,6 +1753,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115734365</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1828,6 +1878,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115734466</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115734662</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2063,6 +2123,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115735183</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2178,6 +2243,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115735661</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2293,6 +2363,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115735802</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116708002</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2516,6 +2596,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119119706</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2636,6 +2721,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131857452</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2756,6 +2846,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860492</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2871,6 +2966,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131861178</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2986,6 +3086,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932494</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3101,6 +3206,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932788</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3208,6 +3318,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933786</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3315,6 +3430,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132670790</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3422,6 +3542,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133140857</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3537,6 +3662,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133430533</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3652,6 +3782,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133701691</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3763,6 +3898,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133701658</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3870,6 +4010,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115734062</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3983,6 +4128,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131856731</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4095,6 +4245,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132670982</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4202,6 +4357,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860402</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4317,6 +4477,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933329</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4432,6 +4597,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131860837</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4543,6 +4713,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133701660</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4654,6 +4829,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133701664</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4751,6 +4931,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69624299</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4848,6 +5033,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69624301</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4945,6 +5135,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69624302</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5057,6 +5252,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131855987</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5175,6 +5375,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131856439</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5293,6 +5498,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131856819</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5405,6 +5615,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931659</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5518,6 +5733,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131935328</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5625,6 +5845,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133139883</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5738,6 +5963,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133526848</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5851,6 +6081,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133701633</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5976,6 +6211,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854070</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6087,6 +6327,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932040</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6207,6 +6452,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933678</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6327,6 +6577,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933889</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6438,6 +6693,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933893</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6549,6 +6809,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933947</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6660,6 +6925,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934032</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6780,8 +7050,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131937568</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>